--- a/output/2026-09-05_09_Italia_Calabria_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-05_09_Italia_Calabria_Utensilerie_e_Macchine_Utensili.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sede a Surbo (LE) ma copertura commerciale su Calabria confermata da pagina dedicata (utcut.com/sandvik-coromant-calabria/) come rivenditore autorizzato Sandvik Coromant.</t>
+          <t>Sede a Surbo (LE) ma copertura commerciale su Calabria confermata da pagina dedicata (utcut.com/sandvik-coromant-calabria/) come rivenditore autorizzato Sandvik Coromant. [DUPLICATO — vedi anche: 2026-09-03_19_Italia_Puglia_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
